--- a/Table11_FYI_BestPractice.xlsx
+++ b/Table11_FYI_BestPractice.xlsx
@@ -386,17 +386,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>0.038</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[-0.104, 0.123]</t>
+          <t>[-0.067, 0.138]</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[-0.469, 0.496]</t>
+          <t>[-0.441, 0.517]</t>
         </is>
       </c>
     </row>
@@ -408,17 +408,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>0.038</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[-0.104, 0.122]</t>
+          <t>[-0.067, 0.137]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[-0.437, 0.459]</t>
+          <t>[-0.414, 0.476]</t>
         </is>
       </c>
     </row>
@@ -462,17 +462,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.029</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[-0.117, 0.119]</t>
+          <t>[-0.084, 0.134]</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[-0.475, 0.482]</t>
+          <t>[-0.451, 0.508]</t>
         </is>
       </c>
     </row>
@@ -484,17 +484,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.029</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[-0.116, 0.119]</t>
+          <t>[-0.084, 0.133]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[-0.443, 0.448]</t>
+          <t>[-0.423, 0.468]</t>
         </is>
       </c>
     </row>
